--- a/06_Test_Metrics/Metrics_Dashboard.xlsx
+++ b/06_Test_Metrics/Metrics_Dashboard.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\ktpm\manual_testing\06_Test_Metrics\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BAFE21-11CE-4FE4-AE32-940BDF14322A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,15 +24,148 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Chỉ số kiểm thử (Metric Name)</t>
+  </si>
+  <si>
+    <t>Công thức tính (Formula)</t>
+  </si>
+  <si>
+    <t>Dữ liệu thực tế</t>
+  </si>
+  <si>
+    <t>Kết quả (Value)</t>
+  </si>
+  <si>
+    <r>
+      <t>Tỷ lệ thực thi test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Test execution rate)</t>
+    </r>
+  </si>
+  <si>
+    <t>(Số TC đã chạy / Tổng số TC) * 100</t>
+  </si>
+  <si>
+    <t>20 / 20</t>
+  </si>
+  <si>
+    <r>
+      <t>Mật độ lỗi theo module</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Defect density)</t>
+    </r>
+  </si>
+  <si>
+    <t>Tổng số lỗi / Tổng số Test Case</t>
+  </si>
+  <si>
+    <t>0.5 bug/TC</t>
+  </si>
+  <si>
+    <r>
+      <t>Phân bố mức độ nghiêm trọng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Severity distribution)</t>
+    </r>
+  </si>
+  <si>
+    <t>(Số lỗi theo từng loại / Tổng số lỗi) * 100</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Critical: 20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Độ bao phủ yêu cầu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Requirement coverage %)</t>
+    </r>
+  </si>
+  <si>
+    <t>(Số yêu cầu đã map TC / Tổng số yêu cầu) * 100</t>
+  </si>
+  <si>
+    <t>• Critical: 2
+• Major: 4
+• Minor: 4</t>
+  </si>
+  <si>
+    <t>10/20</t>
+  </si>
+  <si>
+    <t>8/8</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +176,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -45,12 +184,65 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +522,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="2" max="2" width="38.88671875" customWidth="1"/>
+    <col min="3" max="3" width="35.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.21875" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="47.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="52.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="67.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="8" customFormat="1" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/06_Test_Metrics/Metrics_Dashboard.xlsx
+++ b/06_Test_Metrics/Metrics_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\ktpm\manual_testing\06_Test_Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BAFE21-11CE-4FE4-AE32-940BDF14322A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF3782A-D3E0-4A56-8C3F-EF36DB475BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,111 +42,112 @@
     <t>Kết quả (Value)</t>
   </si>
   <si>
+    <t>Tổng số lỗi / Tổng số Test Case</t>
+  </si>
+  <si>
+    <t>Tỷ lệ thực thi test (Test execution rate)</t>
+  </si>
+  <si>
+    <t>(Số TC đã chạy / Tổng số TC) × 100</t>
+  </si>
+  <si>
+    <t>21 / 21</t>
+  </si>
+  <si>
+    <t>Mật độ lỗi theo module (Defect density)</t>
+  </si>
+  <si>
+    <t>0.52 bug/TC</t>
+  </si>
+  <si>
+    <t>Phân bố mức độ nghiêm trọng (Severity distribution)</t>
+  </si>
+  <si>
+    <t>(Số lỗi theo từng loại / Tổng số lỗi) × 100</t>
+  </si>
+  <si>
+    <t>Độ bao phủ yêu cầu (Requirement coverage %)</t>
+  </si>
+  <si>
+    <t>(Số yêu cầu đã map TC / Tổng số yêu cầu) × 100</t>
+  </si>
+  <si>
+    <t>Critical: 2
+Major: 5
+Minor: 4</t>
+  </si>
+  <si>
     <r>
-      <t>Tỷ lệ thực thi test</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Test execution rate)</t>
-    </r>
-  </si>
-  <si>
-    <t>(Số TC đã chạy / Tổng số TC) * 100</t>
-  </si>
-  <si>
-    <t>20 / 20</t>
-  </si>
-  <si>
-    <r>
-      <t>Mật độ lỗi theo module</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Defect density)</t>
-    </r>
-  </si>
-  <si>
-    <t>Tổng số lỗi / Tổng số Test Case</t>
-  </si>
-  <si>
-    <t>0.5 bug/TC</t>
-  </si>
-  <si>
-    <r>
-      <t>Phân bố mức độ nghiêm trọng</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Severity distribution)</t>
-    </r>
-  </si>
-  <si>
-    <t>(Số lỗi theo từng loại / Tổng số lỗi) * 100</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">• </t>
+      <t xml:space="preserve">Critical: </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>Critical: 20%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Độ bao phủ yêu cầu</t>
+      <t xml:space="preserve">18.18%
+</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> (Requirement coverage %)</t>
+      <t xml:space="preserve">Major: </t>
     </r>
-  </si>
-  <si>
-    <t>(Số yêu cầu đã map TC / Tổng số yêu cầu) * 100</t>
-  </si>
-  <si>
-    <t>• Critical: 2
-• Major: 4
-• Minor: 4</t>
-  </si>
-  <si>
-    <t>10/20</t>
-  </si>
-  <si>
-    <t>8/8</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">45.45%
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Minor: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>36.36%</t>
+    </r>
+  </si>
+  <si>
+    <t>11 / 21</t>
+  </si>
+  <si>
+    <t>9 / 9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,17 +156,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -176,7 +172,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -185,63 +181,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -533,7 +512,7 @@
     <col min="5" max="5" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,71 +529,71 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="47.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+    <row r="2" spans="1:5" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
+      <c r="D3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="52.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="67.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" s="8" customFormat="1" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="5">
         <v>1</v>
       </c>
     </row>
